--- a/review/abilities/workbooks/10_Ancestry_Dwarf.xlsx
+++ b/review/abilities/workbooks/10_Ancestry_Dwarf.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Traits" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pairs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Compare" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Change Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traits" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pairs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compare" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Traits'!$A$4:$L$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Traits'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pairs'!$A$4:$G$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Pairs'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,7 +82,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="007F6000"/>
+      <color rgb="00006100"/>
       <sz val="9"/>
     </font>
     <font>
@@ -116,7 +116,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -188,7 +188,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -225,19 +225,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -730,7 +717,7 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Durable, grounded and craft-minded. Dwarf has the highest HP contribution (+4), the slowest Speed (5), and traits split between combat resilience (Grudge, Stubborn, Rooted) and craft/stone expertise (Maker, Mountain).</t>
+          <t>Durable, grounded and craft-minded. Dwarf has the highest HP contribution (+4), the slowest Speed (5), and traits split between combat resilience (Grudge, Hard as Bedrock, Rooted) and craft/stone expertise (Maker, Stone Mason).</t>
         </is>
       </c>
     </row>
@@ -755,10 +742,10 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
+    <row r="20" ht="46" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock is a bare +1 HP. Maker's Hand and Mountain Remembers are narrow and partly overlap. The ancestry has no social or movement trait, so it can feel one-note outside combat.</t>
+          <t>Hard as Bedrock is intentionally a bare +1 HP; it is the simple durability pick, not a trait with a dramatic moment. Maker's Hand covers portable items and workmanship; Stone Mason covers structures, stone crafting and structural weakness. The ancestry has no social or movement trait, so it can feel one-note outside combat.</t>
         </is>
       </c>
     </row>
@@ -772,7 +759,7 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Give Stubborn a small rider and differentiate Maker/Mountain. If you want a noncombat Dwarf, choose Maker + Mountain; if you want a defender, Grudge + Rooted is the clear pair.</t>
+          <t>Keep Hard as Bedrock simple; differentiate Maker/Stone Mason. If you want a craft/exploration Dwarf, choose Maker + Stone Mason; if you want a defender, Grudge + Rooted is the clear pair.</t>
         </is>
       </c>
     </row>
@@ -818,7 +805,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock</t>
+          <t>Hard as Bedrock</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -867,7 +854,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Combat, Defense, Exploration, Social, Support, Utility</t>
+          <t>Combat, Defense, Exploration, Social, Utility</t>
         </is>
       </c>
     </row>
@@ -884,12 +871,12 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Never Quite Finished, Road in the Blood</t>
+          <t>Never Quite Finished</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Defense, Exploration, Movement, Social, Support, Utility</t>
+          <t>Defense, Exploration, Social, Utility</t>
         </is>
       </c>
     </row>
@@ -930,17 +917,17 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Two pairs of ancestry traits are mechanically identical: Stubborn as Bedrock and Never Quite Finished are both '+1 maximum HP'; Grace of the Elder Folk and Road in the Blood are both '+1 base Speed'.</t>
+          <t>The baseline duplicate stat traits have been differentiated: Hard as Bedrock (+1 maximum HP), Never Quite Finished (+1 maximum HP and a death-mark Boon), Grace of the Elder Folk (+1 Speed) and Adaptable (+1 DP per level).</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Keep the stat but add a small ancestry-specific rider: Dwarf +1 to stabilization or reduce Bleeding after a rest; Human a travel/endurance clause; Elf ignore 1 square of difficult terrain once per scene; Human speed a forced-march benefit.</t>
+          <t>No further action; keep the differentiation.</t>
         </is>
       </c>
     </row>
@@ -1151,13 +1138,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1">
+    <row r="5" ht="41.5" customHeight="1">
       <c r="A5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock</t>
+          <t>Hard as Bedrock</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -1167,12 +1154,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Maximum HP +1. No additional resistance.</t>
+          <t>Maximum HP +1.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Maximum HP +1. Gain no additional resistance from this trait.</t>
+          <t>Maximum HP +1.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1187,12 +1174,12 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>A bare numerical trait and the least evocative Dwarf option. It is efficient but has no moment of its own.</t>
+          <t>Simple, always-on durability. It is intentionally the straightforward ‘tougher dwarf’ pick rather than a trait with a triggered moment.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Add a small rider that feels dwarven: +1 to stabilization, reduce Bleeding by 1 after a rest, or ignore the first point of forced movement each combat. Keep the +1 HP.</t>
+          <t>Approved: positive wording; the +1 HP is the whole benefit.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr"/>
@@ -1203,13 +1190,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
+    <row r="6" ht="66.5" customHeight="1">
       <c r="A6" s="8" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>The Mountain Remembers</t>
+          <t>Stone Mason</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -1219,12 +1206,12 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>1 Boon to examining stonework for an unsafe passage, concealed join or later alteration.</t>
+          <t>1 Boon to examine or craft with stone, including craftsmanship, stone type and origin, patina, secret passages or traps built into stone, and weaknesses in stone structures.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Gain 1 Boon to examining stonework for an unsafe passage, concealed join or later alteration. Obvious construction clues need no roll; the trait does not reveal an untouched wall’s far side.</t>
+          <t>Gain 1 Boon to rolls to examine or craft with stone. This covers judging craftsmanship, recognizing stone type and origin, reading patina or recent toolwork, finding secret passages or traps built into stone, and spotting weaknesses in stone or stone structures. You can identify obvious construction clues without a roll.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1239,12 +1226,12 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Thematic dungeon-delving trait, but narrow and partly overlaps An Honest Maker’s Hand.</t>
+          <t>Broad stone expertise: inspection, crafting and structural weakness. Strong within its niche, and clearly distinct from An Honest Maker’s Hand’s general crafting.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Broaden to any stonework examination, or combine with Maker’s Hand if the two are meant to be one craft identity. Add a clear example of a concealed join.</t>
+          <t>Approved: general stone inspection, stone crafting and structural weakness; obvious construction clues need no roll.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr"/>
@@ -1255,7 +1242,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="41.5" customHeight="1">
+    <row r="7" ht="66.5" customHeight="1">
       <c r="A7" s="7" t="n">
         <v>3</v>
       </c>
@@ -1271,17 +1258,17 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>While standing on solid ground, gain 1 Boon to defense against forced movement.</t>
+          <t>Stability +1. Gain 1 Boon to all Guile rolls.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>While standing on solid ground, gain 1 Boon to defense against forced movement. This is not immunity and does not reduce the resulting distance separately.</t>
+          <t>Stability +1. You gain 1 Boon to Guile rolls.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Defense, Social</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -1291,12 +1278,12 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Good anti-control on a chassis that already has high HP. The 'solid ground' condition gives it a clear fiction.</t>
+          <t>Physical stability plus social stubbornness. Stability +1 is a strong always-on defense; the blanket Guile Boon is the deliberate offset and makes the Dwarf unusually hard to talk out of a position.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify what counts as solid ground (not a ship, ice, mud or while airborne) and whether it applies to collisions as well as pushes.</t>
+          <t>Approved as written: Stability +1 and a blanket Guile Boon; the combination is deliberately strong in both physical control and social scenes.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr"/>
@@ -1323,17 +1310,17 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>After handling an ordinary metal or stone item, recognize shoddy workmanship and common material without a roll; 1 Boon to a consequential inspection for subtler defects.</t>
+          <t>Once per day, after a roll to craft or repair an item, improve the result one step: Weak becomes Standard, or Standard becomes Strong.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>After handling an ordinary metal or stone item, recognize shoddy workmanship and common material without a roll. Gain 1 Boon when a consequential inspection seeks subtler defects. This is not crafting or magical identification permission.</t>
+          <t>Once per day, after you make a roll to craft or repair an item, you may improve the result by one step: Weak becomes Standard, or Standard becomes Strong. A Strong result is unchanged.</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Utility, Social</t>
+          <t>Utility</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1343,12 +1330,12 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Flavorful craft expertise with a no-roll floor and a Boon when it matters. Good for a dwarf who works with their hands.</t>
+          <t>Focused crafting trait: a once-per-day result bump for making or repairing items. It no longer covers inspection or magical identification.</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Specify whether it applies to magical items (text says ordinary only) and add one example of a 'consequential inspection' so DAs know when to call for a roll.</t>
+          <t>Approved: replaced the inspection focus with a once-per-day craft/repair result upgrade. Stone Mason owns stone; An Honest Maker’s Hand owns general crafting.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr"/>
@@ -1359,7 +1346,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9" ht="66.5" customHeight="1">
       <c r="A9" s="7" t="n">
         <v>5</v>
       </c>
@@ -1375,12 +1362,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Once per combat, after a creature damages you, gain 1 Boon to your next attack against it before the end of your next turn.</t>
+          <t>The first creature to deal damage to you in each combat becomes a permanent grudge. Gain 1 Boon to attack rolls against each marked creature; a creature can be marked once, and there is no cap on grudges.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Once per combat, after a creature damages you, gain 1 Boon to your next attack against it before the end of your next turn. Choose whether to invoke the trait when the damage occurs. No damage bonus or extra attack.</t>
+          <t>The first creature that deals damage to you in each combat becomes the mark of your grudge. You gain 1 Boon to attack rolls against each creature marked by your grudge. A creature remains marked forever, even if it escapes. Each creature can be marked once. You can hold any number of grudges.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1395,12 +1382,12 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Reliable retaliation damage; rewards staying in the fight and gives the Dwarf a clear grudge to play.</t>
+          <t>Persistent, campaign-facing grudge. It rewards surviving and remembering, and it is stronger against recurring villains than in one-off fights.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Solid. Clarify whether any damage triggers it (including spells and hazards) and whether the Boon is lost if you do not attack before the end of your next turn.</t>
+          <t>Approved: first creature to damage you each combat becomes a permanent grudge; each creature can be marked once, and there is no cap on grudges.</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr"/>
@@ -1428,15 +1415,12 @@
       <formula>J5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>J5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>J5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="J5:J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1527,7 +1511,7 @@
     <row r="5" ht="41.5" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock + The Mountain Remembers</t>
+          <t>Hard as Bedrock + Stone Mason</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -1542,7 +1526,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock leans defense; The Mountain Remembers leans exploration, utility. Together they cover defense, exploration, utility.</t>
+          <t>Hard as Bedrock leans defense; Stone Mason leans exploration, utility. Together they cover defense, exploration, utility.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -1553,30 +1537,30 @@
       <c r="F5" s="7" t="inlineStr"/>
       <c r="G5" s="7" t="inlineStr"/>
     </row>
-    <row r="6" ht="29" customHeight="1">
+    <row r="6" ht="41.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock + Rooted in Stone</t>
+          <t>Hard as Bedrock + Rooted in Stone</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Defense, Social</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Immovable defender</t>
+          <t>Flexible adventurer</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock leans defense; Rooted in Stone leans defense. Together they cover defense.</t>
+          <t>Hard as Bedrock leans defense; Rooted in Stone leans defense, social. Together they cover defense, social.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Both traits point at the same pillar. Strong specialization; make sure the character has an answer outside it.</t>
+          <t>No obvious anti-synergy; choose for the character story and the campaign's mix of combat, exploration and social scenes.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr"/>
@@ -1585,12 +1569,12 @@
     <row r="7" ht="41.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock + An Honest Maker’s Hand</t>
+          <t>Hard as Bedrock + An Honest Maker’s Hand</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Defense, Social, Utility</t>
+          <t>Defense, Utility</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1600,7 +1584,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock leans defense; An Honest Maker’s Hand leans utility, social. Together they cover defense, social, utility.</t>
+          <t>Hard as Bedrock leans defense; An Honest Maker’s Hand leans utility. Together they cover defense, utility.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1614,7 +1598,7 @@
     <row r="8" ht="29" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock + A Grudge Well Kept</t>
+          <t>Hard as Bedrock + A Grudge Well Kept</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1629,7 +1613,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock leans defense; A Grudge Well Kept leans combat. Together they cover combat, defense.</t>
+          <t>Hard as Bedrock leans defense; A Grudge Well Kept leans combat. Together they cover combat, defense.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1643,12 +1627,12 @@
     <row r="9" ht="41.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>The Mountain Remembers + Rooted in Stone</t>
+          <t>Stone Mason + Rooted in Stone</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Defense, Exploration, Utility</t>
+          <t>Defense, Exploration, Social, Utility</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -1658,12 +1642,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>The Mountain Remembers leans exploration, utility; Rooted in Stone leans defense. Together they cover defense, exploration, utility.</t>
+          <t>Stone Mason leans exploration, utility; Rooted in Stone leans defense, social. Together they cover defense, exploration, social, utility.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>No obvious anti-synergy; choose for the character story and the campaign's mix of combat, exploration and social scenes.</t>
+          <t>Strong out-of-combat pair; check that the character still has a combat contribution.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
@@ -1672,22 +1656,22 @@
     <row r="10" ht="41.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>The Mountain Remembers + An Honest Maker’s Hand</t>
+          <t>Stone Mason + An Honest Maker’s Hand</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Exploration, Social, Utility</t>
+          <t>Exploration, Utility</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Guide and envoy</t>
+          <t>Skill specialist</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>The Mountain Remembers leans exploration, utility; An Honest Maker’s Hand leans utility, social. Together they cover exploration, social, utility.</t>
+          <t>Stone Mason leans exploration, utility; An Honest Maker’s Hand leans utility. Together they cover exploration, utility.</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1701,7 +1685,7 @@
     <row r="11" ht="41.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>The Mountain Remembers + A Grudge Well Kept</t>
+          <t>Stone Mason + A Grudge Well Kept</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1716,7 +1700,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>The Mountain Remembers leans exploration, utility; A Grudge Well Kept leans combat. Together they cover combat, exploration, utility.</t>
+          <t>Stone Mason leans exploration, utility; A Grudge Well Kept leans combat. Together they cover combat, exploration, utility.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -1745,7 +1729,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Rooted in Stone leans defense; An Honest Maker’s Hand leans utility, social. Together they cover defense, social, utility.</t>
+          <t>Rooted in Stone leans defense, social; An Honest Maker’s Hand leans utility. Together they cover defense, social, utility.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1756,7 +1740,7 @@
       <c r="F12" s="8" t="inlineStr"/>
       <c r="G12" s="8" t="inlineStr"/>
     </row>
-    <row r="13" ht="29" customHeight="1">
+    <row r="13" ht="41.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Rooted in Stone + A Grudge Well Kept</t>
@@ -1764,7 +1748,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Combat, Defense</t>
+          <t>Combat, Defense, Social</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1774,7 +1758,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Rooted in Stone leans defense; A Grudge Well Kept leans combat. Together they cover combat, defense.</t>
+          <t>Rooted in Stone leans defense, social; A Grudge Well Kept leans combat. Together they cover combat, defense, social.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -1793,17 +1777,17 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Combat, Social, Utility</t>
+          <t>Combat, Utility</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Battlefield presence</t>
+          <t>Practical fighter</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>An Honest Maker’s Hand leans utility, social; A Grudge Well Kept leans combat. Together they cover combat, social, utility.</t>
+          <t>An Honest Maker’s Hand leans utility; A Grudge Well Kept leans combat. Together they cover combat, utility.</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1831,15 +1815,12 @@
       <formula>F5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>F5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>F5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="F5:F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1956,7 +1937,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock</t>
+          <t>Hard as Bedrock</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2045,7 +2026,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Combat, Defense, Exploration, Social, Support, Utility</t>
+          <t>Combat, Defense, Exploration, Social, Utility</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2082,12 +2063,12 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Never Quite Finished, Road in the Blood</t>
+          <t>Never Quite Finished</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Defense, Exploration, Movement, Social, Support, Utility</t>
+          <t>Defense, Exploration, Social, Utility</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -2118,7 +2099,7 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>• Stubborn as Bedrock and Never Quite Finished are both '+1 maximum HP'; Grace of the Elder Folk and Road in the Blood are both '+1 base Speed'. The mechanics are identical; only the fiction differs (F12).</t>
+          <t>• Hard as Bedrock and Never Quite Finished are both '+1 maximum HP'; Grace of the Elder Folk and Road in the Blood are both '+1 base Speed'. The mechanics are identical; only the fiction differs (F12).</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2182,12 +2163,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="11" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="11" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2268,30 +2248,25 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2315,7 +2290,6 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr"/>
@@ -2335,7 +2309,6 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
@@ -2355,7 +2328,6 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
@@ -2375,7 +2347,6 @@
       <c r="O8" s="8" t="inlineStr"/>
       <c r="P8" s="8" t="inlineStr"/>
       <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr"/>
@@ -2395,7 +2366,6 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr"/>
@@ -2415,7 +2385,6 @@
       <c r="O10" s="8" t="inlineStr"/>
       <c r="P10" s="8" t="inlineStr"/>
       <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr"/>
@@ -2435,7 +2404,6 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr"/>
@@ -2455,7 +2423,6 @@
       <c r="O12" s="8" t="inlineStr"/>
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr"/>
@@ -2475,7 +2442,6 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr"/>
@@ -2495,7 +2461,6 @@
       <c r="O14" s="8" t="inlineStr"/>
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr"/>
@@ -2515,7 +2480,6 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr"/>
@@ -2535,23 +2499,19 @@
       <c r="O16" s="8" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr"/>
       <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
